--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_295_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_295_R30.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7436</v>
+        <v>3.885</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8628</v>
+        <v>3.273</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8809</v>
+        <v>0.612</v>
       </c>
       <c r="G2" t="n">
         <v>2.2221</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1299</v>
+        <v>0.2713</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8259</v>
+        <v>0.2361</v>
       </c>
       <c r="U2" t="n">
-        <v>0.304</v>
+        <v>0.0351</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7138</v>
+        <v>3.5952</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3</v>
+        <v>1.9462</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4137</v>
+        <v>1.649</v>
       </c>
       <c r="G3" t="n">
         <v>1.1311</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2631</v>
+        <v>0.1445</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9006</v>
+        <v>0.5467</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6374</v>
+        <v>-0.4022</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6846</v>
+        <v>3.4813</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7078</v>
+        <v>3.4037</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0232</v>
+        <v>0.0776</v>
       </c>
       <c r="G4" t="n">
         <v>1.2515</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6365</v>
+        <v>0.1601</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1098</v>
+        <v>0.586</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.4259</v>
       </c>
       <c r="V4" t="n">
         <v>0.6778999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7238</v>
+        <v>2.6646</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6918</v>
+        <v>3.4309</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.968</v>
+        <v>-0.7664</v>
       </c>
       <c r="G5" t="n">
         <v>2.2773</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4813</v>
+        <v>-0.5406</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7468</v>
+        <v>-0.0077</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7345</v>
+        <v>-0.5329</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.087</v>
+        <v>2.4392</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2795</v>
+        <v>3.3292</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1925</v>
+        <v>-0.89</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1176</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3315</v>
+        <v>0.0206</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8215</v>
+        <v>0.2282</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.51</v>
+        <v>-0.2076</v>
       </c>
       <c r="V6" t="n">
         <v>1.6083</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6075</v>
+        <v>0.2816</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5171</v>
+        <v>0.1791</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9096</v>
+        <v>0.1025</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9158</v>
+        <v>-0.4683</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2892</v>
+        <v>-1.2547</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6266</v>
+        <v>0.7863</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7321</v>
+        <v>-0.1253</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1547</v>
+        <v>-1.1792</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8868</v>
+        <v>1.0539</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1837</v>
+        <v>-0.343</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4439</v>
+        <v>-0.0755</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7398</v>
+        <v>-0.2676</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>2.276</v>
+        <v>-0.6418</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2492</v>
+        <v>-0.2317</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0268</v>
+        <v>-0.4101</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.409</v>
+        <v>-0.3944</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4107</v>
+        <v>0.2035</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0017</v>
+        <v>-0.5979</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4683</v>
+        <v>-0.7944</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2547</v>
+        <v>-0.0048</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7863</v>
+        <v>-0.7896</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1253</v>
+        <v>0.3529</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1792</v>
+        <v>0.3529</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0539</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.343</v>
+        <v>-1.1473</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0755</v>
+        <v>-0.3577</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2676</v>
+        <v>-0.7896</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3324</v>
+        <v>0.168</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8215</v>
+        <v>-0.1494</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5109</v>
+        <v>0.3174</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4355</v>
+        <v>-0.8026</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1289</v>
+        <v>0.2078</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5643</v>
+        <v>-1.0104</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7944</v>
+        <v>-2.9158</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0048</v>
+        <v>-0.2892</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7896</v>
+        <v>-2.6266</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3529</v>
+        <v>-0.7321</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3529</v>
+        <v>0.1547</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.8868</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1473</v>
+        <v>-2.1837</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3577</v>
+        <v>-0.4439</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7896</v>
+        <v>-1.7398</v>
       </c>
       <c r="P9" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S9" t="n">
-        <v>0.127</v>
+        <v>0.8659</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.224</v>
+        <v>0.9399</v>
       </c>
       <c r="U9" t="n">
-        <v>0.351</v>
+        <v>-0.074</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7116</v>
+        <v>-1.4285</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0611</v>
+        <v>-0.5464</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6505</v>
+        <v>-0.8822</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2594</v>
+        <v>1.9448</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6471</v>
+        <v>0.767</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6122</v>
+        <v>1.1778</v>
       </c>
       <c r="J10" t="n">
-        <v>0.131</v>
+        <v>3.9176</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0574</v>
+        <v>1.3682</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0736</v>
+        <v>2.5495</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3904</v>
+        <v>-1.9729</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7045</v>
+        <v>-0.6012</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6859</v>
+        <v>-1.3717</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4639</v>
+        <v>-4.639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-6.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0117</v>
+        <v>0.1935</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8259</v>
+        <v>0.3501</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1858</v>
+        <v>-0.1566</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3844</v>
+        <v>-1.5709</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0063</v>
+        <v>-0.8868</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3781</v>
+        <v>-0.6841</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9448</v>
+        <v>-1.2594</v>
       </c>
       <c r="H11" t="n">
-        <v>0.767</v>
+        <v>-0.6471</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1778</v>
+        <v>-0.6122</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9176</v>
+        <v>0.131</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3682</v>
+        <v>0.0574</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5495</v>
+        <v>0.0736</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9729</v>
+        <v>-1.3904</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6012</v>
+        <v>-0.7045</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3717</v>
+        <v>-0.6859</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.9585</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2377</v>
+        <v>0.1524</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1098</v>
+        <v>0.0002</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3475</v>
+        <v>0.1522</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2279</v>
+        <v>-2.6381</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.589</v>
+        <v>-2.9992</v>
       </c>
       <c r="F12" t="n">
         <v>0.3611</v>
@@ -1390,10 +1390,10 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0104</v>
+        <v>-0.4206</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7468</v>
+        <v>-0.1571</v>
       </c>
       <c r="U12" t="n">
         <v>-0.2636</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.3919</v>
+        <v>9.512400000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>10.4208</v>
+        <v>11.541</v>
       </c>
       <c r="F13" t="n">
         <v>-2.0288</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1059000000000005</v>
+        <v>-0.105900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9478999999999991</v>
+        <v>0.9478999999999995</v>
       </c>
       <c r="I13" t="n">
         <v>-1.0538</v>
@@ -1447,7 +1447,7 @@
         <v>5.904000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>6.874899999999999</v>
+        <v>6.874900000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-12.8847</v>
@@ -1456,10 +1456,10 @@
         <v>-4.9559</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.928800000000001</v>
+        <v>-7.928799999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>6.958599999999999</v>
+        <v>6.9586</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.4379</v>
@@ -1468,13 +1468,13 @@
         <v>17.3965</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7467000000000001</v>
+        <v>0.3733</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2214</v>
+        <v>2.3413</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.968</v>
+        <v>-1.9682</v>
       </c>
       <c r="V13" t="n">
         <v>2.2862</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8368</v>
+        <v>3.9307</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8183</v>
+        <v>4.4081</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9815</v>
+        <v>-0.4774</v>
       </c>
       <c r="G14" t="n">
         <v>3.8557</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1813</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4832</v>
+        <v>0.1065</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.698</v>
+        <v>-0.1939</v>
       </c>
       <c r="V14" t="n">
         <v>0.3943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8266</v>
+        <v>0.9946</v>
       </c>
       <c r="E15" t="n">
         <v>1.8158</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9892</v>
+        <v>-0.8212</v>
       </c>
       <c r="G15" t="n">
         <v>3.5727</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4266</v>
+        <v>-0.2585</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4086</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.018</v>
+        <v>0.15</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0462</v>
+        <v>0.5208</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4995</v>
+        <v>1.083</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4532</v>
+        <v>-0.5621</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8268</v>
+        <v>-0.1512</v>
       </c>
       <c r="H16" t="n">
-        <v>0.221</v>
+        <v>-0.2483</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0478</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2111</v>
+        <v>1.5466</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6757</v>
+        <v>0.1849</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8868</v>
+        <v>1.3618</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6156</v>
+        <v>-1.6978</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4547</v>
+        <v>-0.4331</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1609</v>
+        <v>-1.2647</v>
       </c>
       <c r="P16" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3215</v>
+        <v>0.118</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1745</v>
+        <v>-0.2317</v>
       </c>
       <c r="U16" t="n">
-        <v>1.147</v>
+        <v>0.3497</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0348</v>
+        <v>0.1167</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0075</v>
+        <v>0.1105</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0274</v>
+        <v>0.0062</v>
       </c>
       <c r="G17" t="n">
         <v>0.1826</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2175</v>
+        <v>-0.0659</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1968</v>
+        <v>0.3148</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4143</v>
+        <v>-0.3806</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>F. FERRARI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2033</v>
+        <v>-0.4216</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4932</v>
+        <v>-0.224</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6965</v>
+        <v>-0.1975</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1512</v>
+        <v>-0.3469</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2483</v>
+        <v>-0.3469</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09710000000000001</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5466</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1849</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3618</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6978</v>
+        <v>-0.3469</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4331</v>
+        <v>-0.3469</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2647</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6062</v>
+        <v>-0.0747</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8215</v>
+        <v>-0.224</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2153</v>
+        <v>0.1494</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. FERRARI</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2871</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.224</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0631</v>
+        <v>0.2681</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3469</v>
+        <v>-3.2418</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3469</v>
+        <v>-1.1104</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-2.1314</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-2.9843</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.6988</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2.2854</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3469</v>
+        <v>-0.2576</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3469</v>
+        <v>-0.4116</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0597</v>
+        <v>-0.2133</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>0.6528</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2838</v>
+        <v>-0.8661</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1569</v>
+        <v>-1.4772</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5117</v>
+        <v>-0.8656</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6452</v>
+        <v>-0.6116</v>
       </c>
       <c r="G20" t="n">
         <v>-0.249</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.3233</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6449</v>
+        <v>0.291</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0013</v>
+        <v>0.0323</v>
       </c>
       <c r="V20" t="n">
         <v>0.5361</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8659</v>
+        <v>-1.8821</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8987</v>
+        <v>-1.1586</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0328</v>
+        <v>-0.7235</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2418</v>
+        <v>-0.8185</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1104</v>
+        <v>-0.156</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1314</v>
+        <v>-0.6625</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.9843</v>
+        <v>0.1072</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6988</v>
+        <v>0.0336</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2854</v>
+        <v>0.0736</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2576</v>
+        <v>-0.9257</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4116</v>
+        <v>-0.1896</v>
       </c>
       <c r="O21" t="n">
-        <v>0.154</v>
+        <v>-0.7361</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3921</v>
+        <v>0.0059</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2908</v>
+        <v>-0.1061</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1013</v>
+        <v>0.112</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6083</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0673</v>
+        <v>-2.1421</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2766</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7907</v>
+        <v>-2.2262</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8185</v>
+        <v>-1.8268</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.156</v>
+        <v>0.221</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6625</v>
+        <v>-2.0478</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1072</v>
+        <v>-0.2111</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0336</v>
+        <v>0.6757</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0736</v>
+        <v>-0.8868</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9257</v>
+        <v>-1.6156</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1896</v>
+        <v>-0.4547</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7361</v>
+        <v>-1.1609</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="R22" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1792</v>
+        <v>1.1332</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.224</v>
+        <v>0.7591</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0448</v>
+        <v>0.3741</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8371</v>
+        <v>-3.3926</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7604</v>
+        <v>0.4066</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5975</v>
+        <v>-3.7992</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4343</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5456</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1325</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5869</v>
+        <v>-0.7885</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3247</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6491</v>
+        <v>-3.9522</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.44</v>
+        <v>-2.6759</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2091</v>
+        <v>-1.2763</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4366</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1792</v>
+        <v>-0.1239</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2715</v>
+        <v>0.0356</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0922</v>
+        <v>-0.1595</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.3919</v>
+        <v>-8.391999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>2.028699999999999</v>
+        <v>2.028900000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.4206</v>
+        <v>-10.4207</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1059000000000001</v>
+        <v>0.1058999999999994</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9482999999999999</v>
+        <v>-0.9483000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0539</v>
+        <v>1.053899999999999</v>
       </c>
       <c r="J25" t="n">
         <v>12.8846</v>
@@ -2383,7 +2383,7 @@
         <v>4.955900000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>7.9289</v>
+        <v>7.928899999999998</v>
       </c>
       <c r="M25" t="n">
         <v>-12.7789</v>
@@ -2392,7 +2392,7 @@
         <v>-5.9041</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.874899999999999</v>
+        <v>-6.8749</v>
       </c>
       <c r="P25" t="n">
         <v>-6.958500000000001</v>
@@ -2404,7 +2404,7 @@
         <v>10.4381</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7467000000000003</v>
+        <v>0.7468</v>
       </c>
       <c r="T25" t="n">
         <v>1.9681</v>
